--- a/examples/HFP_morgan.xlsx
+++ b/examples/HFP_morgan.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Morgan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Morgan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Debts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fixed Assets" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,66 +415,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -529,6 +522,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -567,6 +563,9 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -605,6 +604,9 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -643,6 +645,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -681,6 +686,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -719,6 +727,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -757,6 +768,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -795,6 +809,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -833,6 +850,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -871,6 +891,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -909,6 +932,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -947,6 +973,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -985,6 +1014,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1023,6 +1055,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1061,6 +1096,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1099,6 +1137,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1137,6 +1178,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1175,6 +1219,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1213,6 +1260,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1251,6 +1301,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1289,6 +1342,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1327,6 +1383,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1365,6 +1424,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1403,6 +1465,9 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1441,6 +1506,9 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1479,6 +1547,9 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1517,6 +1588,9 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1555,6 +1629,9 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1593,6 +1670,9 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1631,6 +1711,9 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1669,6 +1752,9 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1707,6 +1793,9 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1745,6 +1834,9 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1783,6 +1875,9 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1821,6 +1916,9 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1859,6 +1957,9 @@
       <c r="L37" t="n">
         <v>0</v>
       </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1897,6 +1998,9 @@
       <c r="L38" t="n">
         <v>0</v>
       </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1935,6 +2039,9 @@
       <c r="L39" t="n">
         <v>0</v>
       </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1973,6 +2080,9 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2011,6 +2121,9 @@
       <c r="L41" t="n">
         <v>0</v>
       </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2049,6 +2162,9 @@
       <c r="L42" t="n">
         <v>0</v>
       </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2087,6 +2203,9 @@
       <c r="L43" t="n">
         <v>0</v>
       </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2123,6 +2242,9 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2141,37 +2263,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
@@ -2192,47 +2314,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>yod</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>

--- a/examples/HFP_morgan.xlsx
+++ b/examples/HFP_morgan.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -519,10 +524,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -560,10 +565,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -601,10 +606,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -642,10 +647,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,10 +688,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -724,10 +729,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -765,10 +770,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -806,10 +811,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -847,10 +852,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,10 +893,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -929,10 +934,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -970,10 +975,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1011,10 +1016,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1052,10 +1057,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1093,10 +1098,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1134,10 +1139,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1175,10 +1180,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1216,10 +1221,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1257,10 +1262,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1298,10 +1303,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1339,10 +1344,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,10 +1385,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1421,10 +1426,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1462,10 +1467,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1503,10 +1508,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1544,10 +1549,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1585,10 +1590,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1626,10 +1631,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1667,10 +1672,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1708,10 +1713,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1749,10 +1754,10 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1790,10 +1795,10 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1831,10 +1836,10 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1872,10 +1877,10 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1913,10 +1918,10 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1954,10 +1959,10 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1995,10 +2000,10 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2036,10 +2041,10 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2077,10 +2082,10 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2118,10 +2123,10 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2159,10 +2164,10 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2200,10 +2205,10 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2241,10 +2246,10 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>0</v>
       </c>
     </row>
